--- a/ExportExcel/Find User Test.xlsx
+++ b/ExportExcel/Find User Test.xlsx
@@ -41,7 +41,7 @@
     <t>FAILED</t>
   </si>
   <si>
-    <t>2096 ms</t>
+    <t>1678 ms</t>
   </si>
   <si>
     <t>User with email containing 'tuong.2274802010979' should be found expected [true] but found [false]</t>
@@ -50,7 +50,7 @@
     <t>testFindUserById</t>
   </si>
   <si>
-    <t>3297 ms</t>
+    <t>1517 ms</t>
   </si>
   <si>
     <t>User with ID 2274802010979 should be found expected [true] but found [false]</t>
@@ -59,7 +59,7 @@
     <t>testFindUserByName</t>
   </si>
   <si>
-    <t>3374 ms</t>
+    <t>1571 ms</t>
   </si>
   <si>
     <t>User with name 'Bui Ke Ton Tuong' should be found expected [true] but found [false]</t>
